--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/SMCH Maternal Outcomes - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/SMCH Maternal Outcomes - metadata.xlsx
@@ -1301,10 +1301,10 @@
         <v>form</v>
       </c>
       <c r="F14" t="str">
-        <v>NeoTreeOutcome</v>
+        <v>NeotreeOutcome</v>
       </c>
       <c r="G14" t="str">
-        <v>Outcome</v>
+        <v>Outcome at discharge</v>
       </c>
       <c r="H14" t="str">
         <v>dropdown</v>
